--- a/CTP_Document_Submittal_Response_DSR_Template.xlsx
+++ b/CTP_Document_Submittal_Response_DSR_Template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,11 @@
       <sz val="11"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
@@ -58,7 +63,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +92,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,6 +137,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin"/>
       <right/>
       <top/>
@@ -160,18 +178,11 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -194,7 +205,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -203,14 +220,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -607,33 +627,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="14" t="n"/>
+      <c r="B1" s="16" t="n"/>
+      <c r="C1" s="16" t="n"/>
+      <c r="D1" s="16" t="n"/>
+      <c r="E1" s="16" t="n"/>
+      <c r="F1" s="16" t="n"/>
+      <c r="G1" s="16" t="n"/>
+      <c r="H1" s="17" t="n"/>
     </row>
     <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="15" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="A2" s="18" t="n"/>
+      <c r="H2" s="19" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="17" t="n"/>
-      <c r="B3" s="18" t="n"/>
-      <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-      <c r="E3" s="19" t="n"/>
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="21" t="n"/>
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="21" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -641,10 +670,13 @@
           <t>DOCUMENT SUBMITTAL RESPONSE / DESIGN SUBMITTAL REVIEW (DSR)</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="20" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="23" t="n"/>
+      <c r="D4" s="23" t="n"/>
+      <c r="E4" s="23" t="n"/>
+      <c r="F4" s="23" t="n"/>
+      <c r="G4" s="23" t="n"/>
+      <c r="H4" s="24" t="n"/>
     </row>
     <row r="5" ht="5" customHeight="1"/>
     <row r="6">
@@ -653,9 +685,11 @@
           <t>PROJECT INFORMATION</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="21" t="n"/>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -663,9 +697,11 @@
           <t>Project Name:</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="21" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
@@ -673,13 +709,15 @@
           <t>Project Number:</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
@@ -687,9 +725,11 @@
           <t>Client:</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="21" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="24" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -697,9 +737,11 @@
           <t>Contractor/Designer:</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11" ht="5" customHeight="1"/>
     <row r="12">
@@ -708,9 +750,11 @@
           <t>SUBMITTAL INFORMATION</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="21" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="24" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -718,13 +762,15 @@
           <t>Submittal Number:</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Revision:</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
@@ -732,9 +778,11 @@
           <t>Document Title:</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="21" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
@@ -742,9 +790,11 @@
           <t>Document Number/Drawing No.:</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="21" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="24" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
@@ -752,13 +802,15 @@
           <t>Date Received:</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Date Reviewed:</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17" ht="5" customHeight="1"/>
     <row r="18">
@@ -767,9 +819,11 @@
           <t>REVIEW STATUS</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="21" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="24" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
@@ -777,13 +831,15 @@
           <t>☐ APPROVED</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>No exceptions taken. Proceed with work.</t>
         </is>
       </c>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="21" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="24" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="B20" s="7" t="inlineStr">
@@ -791,13 +847,15 @@
           <t>☐ APPROVED AS NOTED</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Proceed with work. Incorporate noted corrections.</t>
         </is>
       </c>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="21" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="24" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="7" t="inlineStr">
@@ -805,13 +863,15 @@
           <t>☐ REVISE AND RESUBMIT</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Do not proceed. Make corrections and resubmit.</t>
         </is>
       </c>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="21" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="24" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="B22" s="7" t="inlineStr">
@@ -819,13 +879,15 @@
           <t>☐ REJECTED</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Does not meet requirements. Complete redesign required.</t>
         </is>
       </c>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="21" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="24" t="n"/>
     </row>
     <row r="23" ht="5" customHeight="1"/>
     <row r="24">
@@ -834,14 +896,16 @@
           <t>STRUCTURAL DESIGN REVIEW CHECKLIST</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="21" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="24" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -849,8 +913,10 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -867,8 +933,10 @@
           <t>Design calculations provided and complete</t>
         </is>
       </c>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="6" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="6" t="n"/>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
@@ -881,8 +949,10 @@
           <t>Load combinations comply with applicable codes</t>
         </is>
       </c>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="6" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="B28" s="9" t="inlineStr">
@@ -895,8 +965,10 @@
           <t>Material specifications clearly identified</t>
         </is>
       </c>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="6" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="6" t="n"/>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="B29" s="9" t="inlineStr">
@@ -909,8 +981,10 @@
           <t>Structural drawings are clear and coordinated</t>
         </is>
       </c>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="6" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="B30" s="9" t="inlineStr">
@@ -923,8 +997,10 @@
           <t>Design meets code requirements (IBC, ACI, AISC, etc.)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="6" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="6" t="n"/>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="B31" s="9" t="inlineStr">
@@ -937,8 +1013,10 @@
           <t>Lateral load resisting system adequately designed</t>
         </is>
       </c>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="6" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="6" t="n"/>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="B32" s="9" t="inlineStr">
@@ -951,8 +1029,10 @@
           <t>Foundation design adequate for soil conditions</t>
         </is>
       </c>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="6" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="6" t="n"/>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="B33" s="9" t="inlineStr">
@@ -965,8 +1045,10 @@
           <t>Connection details are adequate and constructible</t>
         </is>
       </c>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="6" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="24" t="n"/>
+      <c r="G33" s="6" t="n"/>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="B34" s="9" t="inlineStr">
@@ -979,8 +1061,10 @@
           <t>Deflection limits are met</t>
         </is>
       </c>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="6" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="24" t="n"/>
+      <c r="G34" s="6" t="n"/>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="B35" s="9" t="inlineStr">
@@ -993,8 +1077,10 @@
           <t>Special inspections requirements identified</t>
         </is>
       </c>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="6" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="24" t="n"/>
+      <c r="G35" s="6" t="n"/>
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="B36" s="9" t="inlineStr">
@@ -1007,8 +1093,10 @@
           <t>Seismic design criteria properly applied</t>
         </is>
       </c>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="6" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="6" t="n"/>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="B37" s="9" t="inlineStr">
@@ -1021,8 +1109,10 @@
           <t>Wind load calculations verified</t>
         </is>
       </c>
-      <c r="D37" s="21" t="n"/>
-      <c r="E37" s="6" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="24" t="n"/>
+      <c r="G37" s="6" t="n"/>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="B38" s="9" t="inlineStr">
@@ -1035,8 +1125,10 @@
           <t>Construction details are practical and buildable</t>
         </is>
       </c>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="6" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="24" t="n"/>
+      <c r="G38" s="6" t="n"/>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="B39" s="9" t="inlineStr">
@@ -1049,8 +1141,10 @@
           <t>All structural elements properly sized</t>
         </is>
       </c>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="6" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="24" t="n"/>
+      <c r="G39" s="6" t="n"/>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="B40" s="9" t="inlineStr">
@@ -1063,8 +1157,10 @@
           <t>Reinforcement details meet code requirements</t>
         </is>
       </c>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="6" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="24" t="n"/>
+      <c r="G40" s="6" t="n"/>
     </row>
     <row r="41" ht="5" customHeight="1"/>
     <row r="42">
@@ -1073,154 +1169,290 @@
           <t>COMMENTS AND OBSERVATIONS</t>
         </is>
       </c>
-      <c r="C42" s="20" t="n"/>
-      <c r="D42" s="20" t="n"/>
-      <c r="E42" s="21" t="n"/>
-    </row>
-    <row r="43" ht="25" customHeight="1">
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="14" t="n"/>
-    </row>
-    <row r="44" ht="25" customHeight="1">
-      <c r="B44" s="15" t="n"/>
-      <c r="E44" s="16" t="n"/>
-    </row>
-    <row r="45" ht="25" customHeight="1">
-      <c r="B45" s="15" t="n"/>
-      <c r="E45" s="16" t="n"/>
-    </row>
-    <row r="46" ht="25" customHeight="1">
-      <c r="B46" s="15" t="n"/>
-      <c r="E46" s="16" t="n"/>
-    </row>
-    <row r="47" ht="25" customHeight="1">
-      <c r="B47" s="15" t="n"/>
-      <c r="E47" s="16" t="n"/>
-    </row>
-    <row r="48" ht="25" customHeight="1">
-      <c r="B48" s="15" t="n"/>
-      <c r="E48" s="16" t="n"/>
-    </row>
-    <row r="49" ht="25" customHeight="1">
-      <c r="B49" s="15" t="n"/>
-      <c r="E49" s="16" t="n"/>
-    </row>
-    <row r="50" ht="25" customHeight="1">
-      <c r="B50" s="15" t="n"/>
-      <c r="E50" s="16" t="n"/>
-    </row>
-    <row r="51" ht="25" customHeight="1">
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="18" t="n"/>
-      <c r="D51" s="18" t="n"/>
-      <c r="E51" s="19" t="n"/>
-    </row>
-    <row r="53" ht="5" customHeight="1"/>
-    <row r="54">
-      <c r="B54" s="3" t="inlineStr">
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="23" t="n"/>
+      <c r="E42" s="23" t="n"/>
+      <c r="F42" s="23" t="n"/>
+      <c r="G42" s="24" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Contractor/Designer Response</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="n"/>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="B44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="24" t="n"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="B45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="12" t="n"/>
+      <c r="G45" s="24" t="n"/>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="B46" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="12" t="n"/>
+      <c r="G46" s="24" t="n"/>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="B47" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="12" t="n"/>
+      <c r="G47" s="24" t="n"/>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="B48" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="12" t="n"/>
+      <c r="G48" s="24" t="n"/>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="B49" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="12" t="n"/>
+      <c r="G49" s="24" t="n"/>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="B50" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="12" t="n"/>
+      <c r="G50" s="24" t="n"/>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="B51" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="12" t="n"/>
+      <c r="G51" s="24" t="n"/>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="B52" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="12" t="n"/>
+      <c r="G52" s="24" t="n"/>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="B53" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="12" t="n"/>
+      <c r="G53" s="24" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>Priority: H=High, M=Medium, L=Low  |  Status: O=Open, C=Closed, P=Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="5" customHeight="1"/>
+    <row r="56">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>REVIEWER INFORMATION</t>
         </is>
       </c>
-      <c r="C54" s="20" t="n"/>
-      <c r="D54" s="20" t="n"/>
-      <c r="E54" s="21" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="B55" s="4" t="inlineStr">
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="23" t="n"/>
+      <c r="F56" s="23" t="n"/>
+      <c r="G56" s="24" t="n"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Reviewed By:</t>
         </is>
       </c>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="21" t="n"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="B56" s="4" t="inlineStr">
+      <c r="C57" s="24" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="23" t="n"/>
+      <c r="F57" s="23" t="n"/>
+      <c r="G57" s="24" t="n"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Title:</t>
         </is>
       </c>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="C58" s="24" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>License No.:</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="B57" s="4" t="inlineStr">
+      <c r="F58" s="24" t="n"/>
+      <c r="G58" s="6" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Signature:</t>
         </is>
       </c>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="21" t="n"/>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="C59" s="24" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="24" t="n"/>
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-    </row>
-    <row r="58" ht="5" customHeight="1"/>
-    <row r="59" ht="15" customHeight="1">
-      <c r="B59" s="11" t="inlineStr">
+      <c r="G59" s="24" t="n"/>
+    </row>
+    <row r="60" ht="5" customHeight="1"/>
+    <row r="61" ht="15" customHeight="1">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>CTP Consulting Engineers</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="B60" s="12" t="inlineStr">
+    <row r="62" ht="15" customHeight="1">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>Structural Engineering Services</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B43:E51"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="A1:E3"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C10:E10"/>
+  <mergeCells count="69">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="F44:G44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
